--- a/data/trans_bre/IP21-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP21-Estudios-trans_bre.xlsx
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 1,85</t>
+          <t>-6,75; 1,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 3,08</t>
+          <t>-5,59; 2,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 6,19</t>
+          <t>-2,54; 6,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,75; 0,0</t>
+          <t>-13,16; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 246,49</t>
+          <t>-100,0; 164,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 219,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 1,07</t>
+          <t>-3,1; 1,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 2,65</t>
+          <t>-1,86; 2,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 1,22</t>
+          <t>-2,3; 1,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 0,87</t>
+          <t>-1,59; 0,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-52,25; 27,27</t>
+          <t>-51,14; 28,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-37,96; 73,44</t>
+          <t>-33,86; 82,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-53,39; 59,45</t>
+          <t>-56,24; 66,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-69,43; 107,7</t>
+          <t>-69,73; 120,92</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 3,42</t>
+          <t>-2,93; 3,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 1,24</t>
+          <t>-5,71; 1,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 4,7</t>
+          <t>-1,64; 4,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,86</t>
+          <t>-0,98; 4,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-62,45; 207,63</t>
+          <t>-62,19; 224,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-82,67; 59,21</t>
+          <t>-82,29; 73,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-41,93; 263,12</t>
+          <t>-45,53; 351,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-68,65; 940,18</t>
+          <t>-63,69; 840,95</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 0,94</t>
+          <t>-2,48; 0,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 1,37</t>
+          <t>-2,19; 1,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,72</t>
+          <t>-1,26; 1,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,86</t>
+          <t>-1,35; 0,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,79; 25,28</t>
+          <t>-46,23; 21,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-40,21; 42,34</t>
+          <t>-40,93; 33,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,15; 81,72</t>
+          <t>-36,15; 77,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-60,74; 88,27</t>
+          <t>-61,2; 82,23</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP21-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP21-Estudios-trans_bre.xlsx
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 1,27</t>
+          <t>-6,61; 1,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 2,4</t>
+          <t>-5,4; 2,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 6,38</t>
+          <t>-2,1; 6,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,16; 0,0</t>
+          <t>-13,17; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 164,02</t>
+          <t>-100,0; 190,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 219,8</t>
+          <t>-100,0; 319,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 1,16</t>
+          <t>-3,29; 1,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 2,75</t>
+          <t>-1,69; 2,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 1,28</t>
+          <t>-2,18; 1,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,95</t>
+          <t>-1,54; 0,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,14; 28,96</t>
+          <t>-53,57; 26,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,86; 82,41</t>
+          <t>-31,45; 84,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-56,24; 66,06</t>
+          <t>-54,59; 61,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-69,73; 120,92</t>
+          <t>-70,49; 106,34</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 3,55</t>
+          <t>-2,71; 3,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 1,25</t>
+          <t>-5,58; 1,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 4,68</t>
+          <t>-1,58; 4,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 4,43</t>
+          <t>-1,28; 3,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-62,19; 224,96</t>
+          <t>-57,23; 240,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-82,29; 73,54</t>
+          <t>-80,82; 63,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-45,53; 351,01</t>
+          <t>-52,44; 269,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-63,69; 840,95</t>
+          <t>-82,63; 742,44</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 0,72</t>
+          <t>-2,66; 0,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 1,26</t>
+          <t>-2,25; 1,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 1,67</t>
+          <t>-1,07; 1,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,82</t>
+          <t>-1,38; 0,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-46,23; 21,07</t>
+          <t>-48,15; 22,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-40,93; 33,66</t>
+          <t>-41,27; 38,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-36,15; 77,76</t>
+          <t>-31,76; 88,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-61,2; 82,23</t>
+          <t>-61,07; 92,61</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP21-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP21-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses</t>
+          <t>Menores que han estado ingresados/as en un hospital en los últimos 12 meses</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-3,41</t>
+          <t>-3,63</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 1,67</t>
+          <t>-6,47; 1,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 2,57</t>
+          <t>-5,51; 3,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 6,56</t>
+          <t>-2,59; 6,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,17; 0,0</t>
+          <t>-16,94; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 190,32</t>
+          <t>-100,0; 246,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 319,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,31</t>
+          <t>-0,27</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-20,8%</t>
+          <t>-18,12%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 1,06</t>
+          <t>-3,31; 1,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 2,83</t>
+          <t>-2,09; 2,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 1,23</t>
+          <t>-2,13; 1,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,85</t>
+          <t>-1,4; 0,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-53,57; 26,42</t>
+          <t>-52,25; 27,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-31,45; 84,97</t>
+          <t>-37,96; 73,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-54,59; 61,74</t>
+          <t>-53,39; 59,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,49; 106,34</t>
+          <t>-68,5; 117,64</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,1</t>
+          <t>1,08</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>79,25%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 3,65</t>
+          <t>-2,86; 3,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 1,17</t>
+          <t>-5,45; 1,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 4,33</t>
+          <t>-1,36; 4,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 3,76</t>
+          <t>-1,08; 3,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-57,23; 240,61</t>
+          <t>-62,45; 207,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-80,82; 63,37</t>
+          <t>-82,67; 59,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-52,44; 269,71</t>
+          <t>-41,93; 263,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-82,63; 742,44</t>
+          <t>-70,62; 978,09</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>-0,21</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-15,08%</t>
+          <t>-12,93%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 0,87</t>
+          <t>-2,42; 0,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 1,39</t>
+          <t>-2,1; 1,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 1,73</t>
+          <t>-1,09; 1,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 0,9</t>
+          <t>-1,24; 0,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-48,15; 22,25</t>
+          <t>-44,79; 25,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-41,27; 38,5</t>
+          <t>-40,21; 42,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,76; 88,49</t>
+          <t>-31,15; 81,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-61,07; 92,61</t>
+          <t>-59,8; 90,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP21-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP21-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,187 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-1,86</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-1,4</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,9</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-3,63</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-48,17%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-37,96%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>145,91%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-1.859457902658656</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.401265338002335</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.895619073945504</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-3.628692669744622</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.4817428306190975</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.379615928859566</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>1.459139680622752</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-6,47; 1,85</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-5,51; 3,08</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-2,59; 6,19</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-16,94; 0,0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 246,49</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-6.466149754151666</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-5.51230795628496</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-2.594799701227732</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-16.93574334683445</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1.853491248124431</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3.079717991750589</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>6.192836697690291</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>2.464917085979919</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-1,06</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,43</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,43</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,27</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-20,58%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,57%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-14,18%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-18,12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-3,31; 1,07</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-2,09; 2,65</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-2,13; 1,22</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-1,4; 0,94</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-52,25; 27,27</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-37,96; 73,44</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-53,39; 59,45</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-68,5; 117,64</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-1.057300721615096</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.4290590645325582</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.4256431414841354</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.2657134501998957</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.2058173991541816</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.09571327276019552</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.1418421306860885</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.1812398968217105</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,45</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-2,04</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,43</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,08</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>13,48%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-43,8%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>52,09%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>79,25%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-3.313268829495122</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-2.090880814836669</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.133477154479344</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-1.397216629937121</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5224949592728714</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.379569871461747</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.5338954451794256</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.6850451907552104</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-2,86; 3,42</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-5,45; 1,24</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-1,36; 4,7</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-1,08; 3,81</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-62,45; 207,63</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-82,67; 59,21</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-41,93; 263,12</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-70,62; 978,09</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.065439615151332</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.645613642675424</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.215675329814542</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0.9388653779874306</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.2727292489456645</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.7344275728511579</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.5944645415347622</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>1.176351000089386</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +807,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,86</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,4</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,24</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,21</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-18,74%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-9,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,65%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-12,93%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.4516278692622916</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-2.044644717048468</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.427969655045013</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.078518734331787</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.1348024651227123</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.4379509330478435</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.520911881316389</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.7924966566420015</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-2,42; 0,94</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,1; 1,37</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-1,09; 1,72</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-1,24; 0,91</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-44,79; 25,28</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-40,21; 42,34</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-31,15; 81,72</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-59,8; 90,19</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-2.86491893866169</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-5.445143065416659</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.357514084939004</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-1.077626155533007</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.6244729229633669</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.826728895203393</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.4193146104250265</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.7062024610063636</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>3.416287245276481</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.237520368613151</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>4.702381275761948</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>3.806846154714154</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>2.076285090525087</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.5921416954822949</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>2.631222883945591</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>9.780909460908527</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.8607624667843837</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.3989420376384806</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.2402932192317277</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.2089621626859904</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.187445175425419</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.08997594728462151</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.08647577327940296</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.1293181965960755</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-2.418760907814518</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.098667440250799</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.087424158193255</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-1.239095873072758</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.4478935398360363</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.4021279926810006</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.3115208350124237</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.5980061108343696</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.9427628260991437</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.367363079325862</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.716591906254494</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.9122228603501382</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.2527622221424825</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.4233530791280948</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.8171663722079819</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.9019051456161002</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1005,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
